--- a/artfynd/A 43992-2022 artfynd.xlsx
+++ b/artfynd/A 43992-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43992-2022 artfynd.xlsx
+++ b/artfynd/A 43992-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99329122</v>
+        <v>99326848</v>
       </c>
       <c r="B2" t="n">
-        <v>56887</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102995</v>
+        <v>102626</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Törnskata</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Lanius collurio</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,14 +710,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>FM-198-1-41, Upl</t>
+          <t>FM-18740-2-36, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672758.7313828423</v>
+        <v>672811</v>
       </c>
       <c r="R2" t="n">
-        <v>6699122.599165405</v>
+        <v>6699213</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,22 +744,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2013-05-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2013-05-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,37 +790,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99322867</v>
+        <v>99329122</v>
       </c>
       <c r="B3" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>102995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,14 +825,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>FM-18462-2-78, Upl</t>
+          <t>FM-198-1-41, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672833.7952755099</v>
+        <v>672759</v>
       </c>
       <c r="R3" t="n">
-        <v>6699191.521473107</v>
+        <v>6699123</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,22 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2004-06-07</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,42 +905,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99329124</v>
+        <v>99329120</v>
       </c>
       <c r="B4" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -959,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672758.7313828423</v>
+        <v>672759</v>
       </c>
       <c r="R4" t="n">
-        <v>6699122.599165405</v>
+        <v>6699123</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1035,42 +1020,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99329127</v>
+        <v>99329124</v>
       </c>
       <c r="B5" t="n">
-        <v>56859</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>103037</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1079,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672758.7313828423</v>
+        <v>672759</v>
       </c>
       <c r="R5" t="n">
-        <v>6699122.599165405</v>
+        <v>6699123</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,22 +1089,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-06-01</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,37 +1135,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99329125</v>
+        <v>99314389</v>
       </c>
       <c r="B6" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103055</v>
+        <v>103042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1195,14 +1170,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>FM-198-1-41, Upl</t>
+          <t>FM-13654-3-26, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672758.7313828423</v>
+        <v>672798</v>
       </c>
       <c r="R6" t="n">
-        <v>6699122.599165405</v>
+        <v>6699111</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1227,9 +1202,10 @@
           <t>Forsmark</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1239,7 +1215,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1275,15 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99369847</v>
+        <v>99322867</v>
       </c>
       <c r="B7" t="n">
-        <v>55981</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,16 +1262,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102964</v>
+        <v>103055</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fiskmås</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Larus canus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1310,19 +1281,19 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>FM-8370-1-62, Upl</t>
+          <t>FM-18462-2-78, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672854.9744089957</v>
+        <v>672834</v>
       </c>
       <c r="R7" t="n">
-        <v>6699184.114762528</v>
+        <v>6699192</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1347,25 +1318,24 @@
           <t>Forsmark</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2018-06-04</t>
+          <t>2004-06-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,6 +1363,223 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>99329125</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>FM-198-1-41, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>672759</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6699123</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2018-06-04</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Mathias Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forsmark platsundersökning</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>86182532</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99026</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219788</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ängsnycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza incarnata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gammelplogarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>672616</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6699084</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Forsmark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43992-2022 artfynd.xlsx
+++ b/artfynd/A 43992-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86182532</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99326848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1004,6 +1019,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329122</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1119,6 +1139,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329120</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1234,6 +1259,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329124</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99314389</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1465,6 +1500,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99322867</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1580,8 +1620,23 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>